--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R3" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275412</v>
+        <v>123275286</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R4" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275279</v>
+        <v>123275396</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582105</v>
+        <v>582047</v>
       </c>
       <c r="R2" t="n">
-        <v>6403532</v>
+        <v>6403578</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275412</v>
+        <v>123275286</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R3" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275396</v>
+        <v>123275412</v>
       </c>
       <c r="B5" t="n">
-        <v>91362</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,12 +1055,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582047</v>
+        <v>582021</v>
       </c>
       <c r="R5" t="n">
-        <v>6403578</v>
+        <v>6403528</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275396</v>
+        <v>123275412</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582047</v>
+        <v>582021</v>
       </c>
       <c r="R2" t="n">
-        <v>6403578</v>
+        <v>6403528</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,7 +792,7 @@
         <v>123275286</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275279</v>
+        <v>123275396</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>91365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582105</v>
+        <v>582047</v>
       </c>
       <c r="R4" t="n">
-        <v>6403532</v>
+        <v>6403578</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275412</v>
+        <v>123275279</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R5" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275412</v>
+        <v>123275286</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R2" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -906,7 +906,7 @@
         <v>123275396</v>
       </c>
       <c r="B4" t="n">
-        <v>91365</v>
+        <v>91367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R5" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R3" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275396</v>
+        <v>123275279</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,12 +941,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582047</v>
+        <v>582105</v>
       </c>
       <c r="R4" t="n">
-        <v>6403578</v>
+        <v>6403532</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275412</v>
+        <v>123275396</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>91373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,13 +1055,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582021</v>
+        <v>582047</v>
       </c>
       <c r="R5" t="n">
-        <v>6403528</v>
+        <v>6403578</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275286</v>
+        <v>123275412</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R2" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275412</v>
+        <v>123275396</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>91376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582021</v>
+        <v>582047</v>
       </c>
       <c r="R3" t="n">
-        <v>6403528</v>
+        <v>6403578</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275279</v>
+        <v>123275286</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275396</v>
+        <v>123275279</v>
       </c>
       <c r="B5" t="n">
-        <v>91373</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,12 +1055,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582047</v>
+        <v>582105</v>
       </c>
       <c r="R5" t="n">
-        <v>6403578</v>
+        <v>6403532</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275412</v>
+        <v>123275286</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R2" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275396</v>
+        <v>123275279</v>
       </c>
       <c r="B3" t="n">
-        <v>91376</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,12 +827,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582047</v>
+        <v>582105</v>
       </c>
       <c r="R3" t="n">
-        <v>6403578</v>
+        <v>6403532</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275286</v>
+        <v>123275396</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>91393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +941,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582105</v>
+        <v>582047</v>
       </c>
       <c r="R4" t="n">
-        <v>6403532</v>
+        <v>6403578</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R5" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123275286</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R3" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -906,7 +906,7 @@
         <v>123275396</v>
       </c>
       <c r="B4" t="n">
-        <v>91393</v>
+        <v>91398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275412</v>
+        <v>123275279</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R5" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -792,7 +792,7 @@
         <v>123275412</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>123275396</v>
       </c>
       <c r="B4" t="n">
-        <v>91398</v>
+        <v>91400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275279</v>
+        <v>123275286</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275279</v>
+        <v>123275286</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275286</v>
+        <v>123275279</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275412</v>
+        <v>123275396</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>91400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582021</v>
+        <v>582047</v>
       </c>
       <c r="R3" t="n">
-        <v>6403528</v>
+        <v>6403578</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123275396</v>
+        <v>123275286</v>
       </c>
       <c r="B4" t="n">
-        <v>91400</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,12 +941,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582047</v>
+        <v>582105</v>
       </c>
       <c r="R4" t="n">
-        <v>6403578</v>
+        <v>6403532</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275279</v>
+        <v>123275412</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582105</v>
+        <v>582021</v>
       </c>
       <c r="R5" t="n">
-        <v>6403532</v>
+        <v>6403528</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 10781-2025 artfynd.xlsx
+++ b/artfynd/A 10781-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123275279</v>
+        <v>123275396</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582105</v>
+        <v>582047</v>
       </c>
       <c r="R2" t="n">
-        <v>6403532</v>
+        <v>6403578</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123275396</v>
+        <v>123275412</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,12 +817,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582047</v>
+        <v>582021</v>
       </c>
       <c r="R3" t="n">
-        <v>6403578</v>
+        <v>6403528</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,12 +896,7 @@
         <v>123275286</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123275412</v>
+        <v>123275279</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,7 +1039,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582021</v>
+        <v>582105</v>
       </c>
       <c r="R5" t="n">
-        <v>6403528</v>
+        <v>6403532</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
